--- a/inst/extdata/example_anq_template.xlsx
+++ b/inst/extdata/example_anq_template.xlsx
@@ -10,7 +10,8 @@
     <sheet name="MB - Minimales Datenset" sheetId="1" r:id="rId1"/>
     <sheet name="MP - Psychiatrie Zusatzdaten" sheetId="2" r:id="rId2"/>
     <sheet name="PH - HoNOS" sheetId="3" r:id="rId3"/>
-    <sheet name="FM - Freiheitsbeschränkende M" sheetId="4" r:id="rId4"/>
+    <sheet name="PB - BSCL" sheetId="4" r:id="rId4"/>
+    <sheet name="FM - Freiheitsbeschränkende M" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2455,6 +2456,1322 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:BH15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>V4</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>V9</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>V11</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>V12</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>V13</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>V15</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>V16</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>V17</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>V18</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>V19</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>V20</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>V21</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>V22</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>V23</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>V24</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>V25</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>V26</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>V27</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>V28</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>V29</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>V30</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>V31</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>V32</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>V33</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>V34</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>V35</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>V36</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>V37</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>V40</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>V41</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>V42</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>V43</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>V44</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>V45</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>V46</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>V47</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>V48</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>V49</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>V50</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>V51</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>V52</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>V53</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>V54</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>V55</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>V56</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>V57</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>V58</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>V59</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>V60</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ab hier Eingabe</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>5050286</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>20120730</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5050286</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>20120806</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5050297</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>20120103</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5050297</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>20120226</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5050292</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>forensic psychiatry, exempt from BSCL since 01.07.2019</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>20121223</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>5050292</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>forensic psychiatry, exempt from BSCL since 01.07.2019</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>20121231</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
